--- a/Assignment 1/A1.xlsx
+++ b/Assignment 1/A1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sloane\OneDrive\Desktop\UT\Financial Analytics\Assignments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sloane\OneDrive\Desktop\UT\financial_analytics\financial_analytics_assignments\Assignment 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EC5920-7272-456B-80F9-667A447B162D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9812D368-C8CD-4D72-AD86-AB6DC079E693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9846" yWindow="0" windowWidth="13272" windowHeight="13758" xr2:uid="{44C43571-FD71-41B3-BE7A-AFF9CCA37847}"/>
+    <workbookView xWindow="12192" yWindow="0" windowWidth="10926" windowHeight="13758" xr2:uid="{44C43571-FD71-41B3-BE7A-AFF9CCA37847}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -178,17 +178,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -200,13 +215,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,17 +565,17 @@
     <col min="4" max="4" width="25.15625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="10" customFormat="1" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -614,10 +629,10 @@
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="8">
         <v>463193.49</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="6" t="s">
         <v>24</v>
       </c>
     </row>
@@ -638,7 +653,7 @@
       <c r="B10" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>350000</v>
       </c>
     </row>
@@ -649,7 +664,7 @@
       <c r="B11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="9">
         <f>(C12/C10)^(1/C13)-1</f>
         <v>0.11069085371075271</v>
       </c>
@@ -704,10 +719,10 @@
       <c r="A17" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>3333333</v>
       </c>
     </row>
@@ -726,10 +741,10 @@
       <c r="A19" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>100000000</v>
       </c>
     </row>
@@ -740,7 +755,7 @@
       <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="8">
         <f>C17*((1-(1.05)^-30)/0.05)</f>
         <v>51241498.298792444</v>
       </c>
@@ -773,10 +788,10 @@
       <c r="A24" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>3333333</v>
       </c>
     </row>
@@ -787,7 +802,7 @@
       <c r="B25" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="9">
         <f>RATE(30,-3333333,47000000)</f>
         <v>5.7767469729529203E-2</v>
       </c>
@@ -796,8 +811,11 @@
       <c r="A26" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="C26" s="5">
+        <v>100000000</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -807,7 +825,7 @@
       <c r="B27" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>47000000</v>
       </c>
     </row>
@@ -828,7 +846,7 @@
       <c r="B30" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="4">
         <v>1000</v>
       </c>
     </row>
@@ -861,7 +879,9 @@
       <c r="B33" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="8"/>
+      <c r="C33" s="10">
+        <v>16618.439999999999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
